--- a/Eksperymenty.xlsx
+++ b/Eksperymenty.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mateu\OneDrive\Pulpit\PG przedmioty\2 stopien\sem1\MSI_projekt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F68AAC15-BEBD-40DD-94FD-EE9003C0B483}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{343494B2-99B1-4C61-9618-E5B6600CC31B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{37F6EF12-67D2-4258-93BE-F0B77882A1C3}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="14">
   <si>
     <t>numer testu</t>
   </si>
@@ -61,32 +61,22 @@
   </si>
   <si>
     <t>retinanet_resnet50_fpn</t>
+  </si>
+  <si>
+    <t>fasterrcnn_resnet50_fpn_v2</t>
+  </si>
+  <si>
+    <t>fcos_resnet50_fpn</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="238"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="238"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C5700"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="238"/>
@@ -100,22 +90,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -127,20 +107,14 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2"/>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="Neutralny" xfId="2" builtinId="28"/>
+  <cellStyles count="1">
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
-    <cellStyle name="Zły" xfId="1" builtinId="27"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -452,13 +426,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4D367A2-F224-429C-ABD2-A138AA583EAF}">
-  <dimension ref="B2:H11"/>
+  <dimension ref="B2:H18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="33.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="71.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
@@ -485,25 +463,25 @@
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="1">
+      <c r="B3">
         <v>1</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="1">
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3">
         <v>1E-3</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F3">
         <v>5</v>
       </c>
-      <c r="G3" s="1">
-        <v>8</v>
-      </c>
-      <c r="H3" s="1">
+      <c r="G3">
+        <v>8</v>
+      </c>
+      <c r="H3">
         <v>5.0000000000000001E-4</v>
       </c>
     </row>
@@ -531,25 +509,25 @@
       </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B5" s="2">
+      <c r="B5">
         <v>3</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E5" s="2">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="F5" s="2">
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>0.01</v>
+      </c>
+      <c r="F5">
         <v>5</v>
       </c>
-      <c r="G5" s="2">
-        <v>8</v>
-      </c>
-      <c r="H5" s="2">
+      <c r="G5">
+        <v>8</v>
+      </c>
+      <c r="H5">
         <v>5.0000000000000001E-4</v>
       </c>
     </row>
@@ -561,13 +539,13 @@
         <v>8</v>
       </c>
       <c r="D6" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>1E-4</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G6">
         <v>8</v>
@@ -587,7 +565,7 @@
         <v>7</v>
       </c>
       <c r="E7">
-        <v>5.0000000000000001E-4</v>
+        <v>1E-4</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -607,13 +585,13 @@
         <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E8">
-        <v>5.0000000000000001E-3</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="F8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G8">
         <v>8</v>
@@ -627,16 +605,16 @@
         <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E9">
-        <v>5.0000000000000001E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="F9">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G9">
         <v>8</v>
@@ -650,16 +628,16 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D10" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E10">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="F10">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="G10">
         <v>8</v>
@@ -691,8 +669,169 @@
         <v>5.0000000000000001E-4</v>
       </c>
     </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B12">
+        <v>10</v>
+      </c>
+      <c r="C12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" t="s">
+        <v>2</v>
+      </c>
+      <c r="E12">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="F12">
+        <v>10</v>
+      </c>
+      <c r="G12">
+        <v>8</v>
+      </c>
+      <c r="H12">
+        <v>5.0000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B13">
+        <v>11</v>
+      </c>
+      <c r="C13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" t="s">
+        <v>2</v>
+      </c>
+      <c r="E13">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="F13">
+        <v>25</v>
+      </c>
+      <c r="G13">
+        <v>8</v>
+      </c>
+      <c r="H13">
+        <v>5.0000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B14">
+        <v>12</v>
+      </c>
+      <c r="C14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E14">
+        <v>2E-3</v>
+      </c>
+      <c r="F14">
+        <v>25</v>
+      </c>
+      <c r="G14">
+        <v>8</v>
+      </c>
+      <c r="H14">
+        <v>5.0000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B15">
+        <v>13</v>
+      </c>
+      <c r="C15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" t="s">
+        <v>2</v>
+      </c>
+      <c r="E15">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="F15">
+        <v>25</v>
+      </c>
+      <c r="G15">
+        <v>8</v>
+      </c>
+      <c r="H15">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <v>14</v>
+      </c>
+      <c r="C16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" t="s">
+        <v>2</v>
+      </c>
+      <c r="E16">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="F16">
+        <v>10</v>
+      </c>
+      <c r="G16">
+        <v>8</v>
+      </c>
+      <c r="H16">
+        <v>5.0000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <v>15</v>
+      </c>
+      <c r="C17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E17">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="F17">
+        <v>10</v>
+      </c>
+      <c r="G17">
+        <v>8</v>
+      </c>
+      <c r="H17">
+        <v>5.0000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18">
+        <v>16</v>
+      </c>
+      <c r="C18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" t="s">
+        <v>2</v>
+      </c>
+      <c r="E18">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="F18">
+        <v>10</v>
+      </c>
+      <c r="G18">
+        <v>8</v>
+      </c>
+      <c r="H18">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>